--- a/Results/yearly_results.xlsx
+++ b/Results/yearly_results.xlsx
@@ -460,16 +460,16 @@
         <v>2029</v>
       </c>
       <c r="B2" t="n">
-        <v>330834.2411835876</v>
+        <v>367981.3001621086</v>
       </c>
       <c r="C2" t="n">
-        <v>165353.5682168572</v>
+        <v>163996.0930712459</v>
       </c>
       <c r="D2" t="n">
-        <v>1712558.365509629</v>
+        <v>1691545.226246618</v>
       </c>
       <c r="E2" t="n">
-        <v>2208746.174910074</v>
+        <v>2223522.619479972</v>
       </c>
     </row>
     <row r="3">
@@ -477,16 +477,16 @@
         <v>2030</v>
       </c>
       <c r="B3" t="n">
-        <v>334802.9117041813</v>
+        <v>379399.8512700354</v>
       </c>
       <c r="C3" t="n">
-        <v>153569.6165639875</v>
+        <v>153907.7662519316</v>
       </c>
       <c r="D3" t="n">
-        <v>1715772.386279526</v>
+        <v>1689075.207859201</v>
       </c>
       <c r="E3" t="n">
-        <v>2204144.914547695</v>
+        <v>2222382.825381168</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2031</v>
       </c>
       <c r="B4" t="n">
-        <v>330531.2285995443</v>
+        <v>387623.2468893439</v>
       </c>
       <c r="C4" t="n">
-        <v>128741.7117074145</v>
+        <v>129988.5120099083</v>
       </c>
       <c r="D4" t="n">
-        <v>1737778.576115768</v>
+        <v>1700656.079271965</v>
       </c>
       <c r="E4" t="n">
-        <v>2197051.516422727</v>
+        <v>2218267.838171218</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>2032</v>
       </c>
       <c r="B5" t="n">
-        <v>324202.670616503</v>
+        <v>386413.0365253857</v>
       </c>
       <c r="C5" t="n">
-        <v>129716.3979455767</v>
+        <v>129908.5577248477</v>
       </c>
       <c r="D5" t="n">
-        <v>1747800.136581174</v>
+        <v>1709686.870640048</v>
       </c>
       <c r="E5" t="n">
-        <v>2201719.205143254</v>
+        <v>2226008.464890282</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>2033</v>
       </c>
       <c r="B6" t="n">
-        <v>328428.099831914</v>
+        <v>400145.0940394124</v>
       </c>
       <c r="C6" t="n">
-        <v>119826.9090548989</v>
+        <v>122938.1403004414</v>
       </c>
       <c r="D6" t="n">
-        <v>1745762.224731192</v>
+        <v>1699153.472194043</v>
       </c>
       <c r="E6" t="n">
-        <v>2194017.233618005</v>
+        <v>2222236.706533897</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>2034</v>
       </c>
       <c r="B7" t="n">
-        <v>327197.5014861019</v>
+        <v>405141.2810093225</v>
       </c>
       <c r="C7" t="n">
-        <v>107861.5777840985</v>
+        <v>112242.4290457211</v>
       </c>
       <c r="D7" t="n">
-        <v>1754142.25003718</v>
+        <v>1702536.906913128</v>
       </c>
       <c r="E7" t="n">
-        <v>2189201.329307381</v>
+        <v>2219920.616968172</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>2035</v>
       </c>
       <c r="B8" t="n">
-        <v>326489.768015653</v>
+        <v>418266.5131117235</v>
       </c>
       <c r="C8" t="n">
-        <v>94317.98516435776</v>
+        <v>99506.23184394592</v>
       </c>
       <c r="D8" t="n">
-        <v>1764390.465231319</v>
+        <v>1701653.698514428</v>
       </c>
       <c r="E8" t="n">
-        <v>2185198.21841133</v>
+        <v>2219426.443470098</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>2036</v>
       </c>
       <c r="B9" t="n">
-        <v>321107.4829214674</v>
+        <v>419659.2795446474</v>
       </c>
       <c r="C9" t="n">
-        <v>86112.83895710141</v>
+        <v>95867.28065175108</v>
       </c>
       <c r="D9" t="n">
-        <v>1780960.703479365</v>
+        <v>1709693.505946802</v>
       </c>
       <c r="E9" t="n">
-        <v>2188181.025357935</v>
+        <v>2225220.066143201</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>2037</v>
       </c>
       <c r="B10" t="n">
-        <v>323422.2166554201</v>
+        <v>425121.5887610595</v>
       </c>
       <c r="C10" t="n">
-        <v>74421.10249268921</v>
+        <v>79472.70152990337</v>
       </c>
       <c r="D10" t="n">
-        <v>1784964.566167146</v>
+        <v>1718159.670764943</v>
       </c>
       <c r="E10" t="n">
-        <v>2182807.885315256</v>
+        <v>2222753.961055906</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>2038</v>
       </c>
       <c r="B11" t="n">
-        <v>319423.3098144754</v>
+        <v>423361.4342415439</v>
       </c>
       <c r="C11" t="n">
-        <v>72009.02463526947</v>
+        <v>73881.81954036748</v>
       </c>
       <c r="D11" t="n">
-        <v>1788120.554399935</v>
+        <v>1725960.581823414</v>
       </c>
       <c r="E11" t="n">
-        <v>2179552.88884968</v>
+        <v>2223203.835605325</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>2039</v>
       </c>
       <c r="B12" t="n">
-        <v>316488.1413281015</v>
+        <v>432737.6472799116</v>
       </c>
       <c r="C12" t="n">
-        <v>59232.41469237107</v>
+        <v>64079.57561507441</v>
       </c>
       <c r="D12" t="n">
-        <v>1800167.091817478</v>
+        <v>1725568.888129754</v>
       </c>
       <c r="E12" t="n">
-        <v>2175887.647837951</v>
+        <v>2222386.11102474</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>2040</v>
       </c>
       <c r="B13" t="n">
-        <v>316653.0662271102</v>
+        <v>435774.8378075849</v>
       </c>
       <c r="C13" t="n">
-        <v>54010.2628133679</v>
+        <v>58123.90350570701</v>
       </c>
       <c r="D13" t="n">
-        <v>1808796.212199359</v>
+        <v>1735367.149229049</v>
       </c>
       <c r="E13" t="n">
-        <v>2179459.541239837</v>
+        <v>2229265.890542341</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>2041</v>
       </c>
       <c r="B14" t="n">
-        <v>314653.2132956228</v>
+        <v>453085.3930612354</v>
       </c>
       <c r="C14" t="n">
-        <v>48844.74329824807</v>
+        <v>54895.95811366334</v>
       </c>
       <c r="D14" t="n">
-        <v>1806693.377683258</v>
+        <v>1715795.219071094</v>
       </c>
       <c r="E14" t="n">
-        <v>2170191.334277128</v>
+        <v>2223776.570245993</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>2042</v>
       </c>
       <c r="B15" t="n">
-        <v>302621.2348728221</v>
+        <v>450784.7010244196</v>
       </c>
       <c r="C15" t="n">
-        <v>33076.45284282813</v>
+        <v>37385.62361238663</v>
       </c>
       <c r="D15" t="n">
-        <v>1830398.844107545</v>
+        <v>1737016.553897789</v>
       </c>
       <c r="E15" t="n">
-        <v>2166096.531823196</v>
+        <v>2225186.878534595</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>2043</v>
       </c>
       <c r="B16" t="n">
-        <v>313015.2094635528</v>
+        <v>462310.2680008779</v>
       </c>
       <c r="C16" t="n">
-        <v>34977.00130145003</v>
+        <v>38111.68604541153</v>
       </c>
       <c r="D16" t="n">
-        <v>1818156.749586472</v>
+        <v>1729361.623765002</v>
       </c>
       <c r="E16" t="n">
-        <v>2166148.960351475</v>
+        <v>2229783.577811291</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>2044</v>
       </c>
       <c r="B17" t="n">
-        <v>308404.0878347412</v>
+        <v>463721.625895967</v>
       </c>
       <c r="C17" t="n">
-        <v>17031.61875667034</v>
+        <v>20085.13838921995</v>
       </c>
       <c r="D17" t="n">
-        <v>1839659.929590359</v>
+        <v>1746402.192234181</v>
       </c>
       <c r="E17" t="n">
-        <v>2165095.636181771</v>
+        <v>2230208.956519368</v>
       </c>
     </row>
   </sheetData>
